--- a/plantilla-base.xlsx
+++ b/plantilla-base.xlsx
@@ -16,7 +16,7 @@
     <sheet name="Almacenes" sheetId="7" r:id="rId10"/>
   </sheets>
   <definedNames>
-    <definedName name="catalogo_category_slugs">'Categorias'!$A$2:$A$100</definedName>
+    <definedName name="catalogo_category_slugs">'Categorias'!$A$2:$A$21</definedName>
     <definedName name="catalogo_tag_slugs">'Tags'!$A$2:$A$2</definedName>
     <definedName name="valores_condition">'Valores'!$A$2:$A$3</definedName>
     <definedName name="valores_status">'Valores'!$B$2:$B$3</definedName>
@@ -521,7 +521,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="291">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="127">
   <si>
     <t>Código de ubicación</t>
   </si>
@@ -796,556 +796,64 @@
     <t>name</t>
   </si>
   <si>
-    <t>accesorios</t>
+    <t>Accesorios-Bano</t>
   </si>
   <si>
-    <t>Accesorios</t>
+    <t>Accesorios-Bebe</t>
   </si>
   <si>
-    <t>accesorios-de-cama</t>
+    <t>Accesorios-Cocina</t>
   </si>
   <si>
-    <t>Accesorios de cama</t>
+    <t>Accesorios-Dormitorio</t>
   </si>
   <si>
-    <t>accesorios-de-cocina</t>
+    <t>Accesorios-Hogar</t>
   </si>
   <si>
-    <t>Accesorios de cocina</t>
+    <t>Accesorios-Hombre</t>
   </si>
   <si>
-    <t>accesorios-de-gimnasio</t>
+    <t>Accesorios-Mujer</t>
   </si>
   <si>
-    <t>Accesorios de gimnasio</t>
+    <t>Accesorios-Ninos</t>
   </si>
   <si>
-    <t>accesorios-para-automovil</t>
+    <t>Accesorios-Personales</t>
   </si>
   <si>
-    <t>Accesorios para automóvil</t>
+    <t>Accesorios-Sala</t>
   </si>
   <si>
-    <t>accesorios-para-instrumentos</t>
-  </si>
-  <si>
-    <t>Accesorios para instrumentos</t>
-  </si>
-  <si>
-    <t>accesorios-para-motocicleta</t>
-  </si>
-  <si>
-    <t>Accesorios para motocicleta</t>
-  </si>
-  <si>
-    <t>accesorios-para-sala</t>
-  </si>
-  <si>
-    <t>Accesorios para sala</t>
-  </si>
-  <si>
-    <t>accesorios-para-videojuegos</t>
-  </si>
-  <si>
-    <t>Accesorios para videojuegos</t>
-  </si>
-  <si>
-    <t>adultos</t>
-  </si>
-  <si>
-    <t>Adultos</t>
-  </si>
-  <si>
-    <t>audio</t>
-  </si>
-  <si>
-    <t>Audio</t>
-  </si>
-  <si>
-    <t>automotriz</t>
-  </si>
-  <si>
-    <t>Automotriz</t>
-  </si>
-  <si>
-    <t>autopartes</t>
-  </si>
-  <si>
-    <t>Autopartes</t>
-  </si>
-  <si>
-    <t>bebe</t>
-  </si>
-  <si>
-    <t>Bebé</t>
-  </si>
-  <si>
-    <t>belleza</t>
-  </si>
-  <si>
-    <t>Belleza</t>
-  </si>
-  <si>
-    <t>cables</t>
-  </si>
-  <si>
-    <t>Cables</t>
-  </si>
-  <si>
-    <t>calzado</t>
+    <t>Accesorios-Unisex</t>
   </si>
   <si>
     <t>Calzado</t>
   </si>
   <si>
-    <t>carpinteria</t>
+    <t>Calzado-Bebe</t>
   </si>
   <si>
-    <t>Carpintería</t>
+    <t>Calzado-Hombre</t>
   </si>
   <si>
-    <t>cascos</t>
+    <t>Calzado-Mujer</t>
   </si>
   <si>
-    <t>Cascos</t>
-  </si>
-  <si>
-    <t>ciclismo</t>
-  </si>
-  <si>
-    <t>Ciclismo</t>
-  </si>
-  <si>
-    <t>collares</t>
-  </si>
-  <si>
-    <t>Collares</t>
-  </si>
-  <si>
-    <t>computacion</t>
-  </si>
-  <si>
-    <t>Computación</t>
-  </si>
-  <si>
-    <t>conjuntos-deportivos</t>
-  </si>
-  <si>
-    <t>Conjuntos deportivos</t>
-  </si>
-  <si>
-    <t>conjuntos-para-motociclista</t>
-  </si>
-  <si>
-    <t>Conjuntos para motociclista</t>
-  </si>
-  <si>
-    <t>consolas</t>
-  </si>
-  <si>
-    <t>Consolas</t>
-  </si>
-  <si>
-    <t>controles</t>
-  </si>
-  <si>
-    <t>Controles</t>
-  </si>
-  <si>
-    <t>cuidado-capilar</t>
-  </si>
-  <si>
-    <t>Cuidado capilar</t>
-  </si>
-  <si>
-    <t>dental</t>
-  </si>
-  <si>
-    <t>Dental</t>
-  </si>
-  <si>
-    <t>deportes</t>
-  </si>
-  <si>
-    <t>Deportes</t>
-  </si>
-  <si>
-    <t>discos-duros</t>
-  </si>
-  <si>
-    <t>Discos duros</t>
-  </si>
-  <si>
-    <t>disfraces</t>
-  </si>
-  <si>
-    <t>Disfraces</t>
-  </si>
-  <si>
-    <t>electricidad</t>
-  </si>
-  <si>
-    <t>Electricidad</t>
-  </si>
-  <si>
-    <t>electronica</t>
-  </si>
-  <si>
-    <t>Electrónica</t>
-  </si>
-  <si>
-    <t>escolar</t>
-  </si>
-  <si>
-    <t>Escolar</t>
-  </si>
-  <si>
-    <t>estuches</t>
-  </si>
-  <si>
-    <t>Estuches</t>
-  </si>
-  <si>
-    <t>gadgets</t>
-  </si>
-  <si>
-    <t>Gadgets</t>
-  </si>
-  <si>
-    <t>gatos</t>
-  </si>
-  <si>
-    <t>Gatos</t>
-  </si>
-  <si>
-    <t>halloween</t>
-  </si>
-  <si>
-    <t>Halloween</t>
-  </si>
-  <si>
-    <t>herramientas</t>
-  </si>
-  <si>
-    <t>Herramientas</t>
-  </si>
-  <si>
-    <t>hogar</t>
+    <t>Calzado-Ninos</t>
   </si>
   <si>
     <t>Hogar</t>
   </si>
   <si>
-    <t>hombre</t>
+    <t>Limpieza-Hogar</t>
   </si>
   <si>
-    <t>Hombre</t>
+    <t>Muebles-Armables</t>
   </si>
   <si>
-    <t>iluminacion</t>
-  </si>
-  <si>
-    <t>Iluminación</t>
-  </si>
-  <si>
-    <t>instrumentos</t>
-  </si>
-  <si>
-    <t>Instrumentos</t>
-  </si>
-  <si>
-    <t>jardineria</t>
-  </si>
-  <si>
-    <t>Jardinería</t>
-  </si>
-  <si>
-    <t>joyeria</t>
-  </si>
-  <si>
-    <t>Joyería</t>
-  </si>
-  <si>
-    <t>juguetes</t>
-  </si>
-  <si>
-    <t>Juguetes</t>
-  </si>
-  <si>
-    <t>juguetes-sexuales</t>
-  </si>
-  <si>
-    <t>Juguetes sexuales</t>
-  </si>
-  <si>
-    <t>lamparas</t>
-  </si>
-  <si>
-    <t>Lámparas</t>
-  </si>
-  <si>
-    <t>lamparas-de-mano</t>
-  </si>
-  <si>
-    <t>Lámparas de mano</t>
-  </si>
-  <si>
-    <t>lamparas-de-techo</t>
-  </si>
-  <si>
-    <t>Lámparas de techo</t>
-  </si>
-  <si>
-    <t>lapiceras</t>
-  </si>
-  <si>
-    <t>Lapiceras</t>
-  </si>
-  <si>
-    <t>led-para-automovil</t>
-  </si>
-  <si>
-    <t>LED para automóvil</t>
-  </si>
-  <si>
-    <t>led-para-motocicleta</t>
-  </si>
-  <si>
-    <t>LED para motocicleta</t>
-  </si>
-  <si>
-    <t>lenceria</t>
-  </si>
-  <si>
-    <t>Lencería</t>
-  </si>
-  <si>
-    <t>loncheras</t>
-  </si>
-  <si>
-    <t>Loncheras</t>
-  </si>
-  <si>
-    <t>luces-de-exterior</t>
-  </si>
-  <si>
-    <t>Luces de exterior</t>
-  </si>
-  <si>
-    <t>luces-led</t>
-  </si>
-  <si>
-    <t>Luces LED</t>
-  </si>
-  <si>
-    <t>maquillaje</t>
-  </si>
-  <si>
-    <t>Maquillaje</t>
-  </si>
-  <si>
-    <t>mascotas</t>
-  </si>
-  <si>
-    <t>Mascotas</t>
-  </si>
-  <si>
-    <t>medicina</t>
-  </si>
-  <si>
-    <t>Medicina</t>
-  </si>
-  <si>
-    <t>medicina-naturista</t>
-  </si>
-  <si>
-    <t>Medicina naturista</t>
-  </si>
-  <si>
-    <t>medico</t>
-  </si>
-  <si>
-    <t>Médico</t>
-  </si>
-  <si>
-    <t>memorias</t>
-  </si>
-  <si>
-    <t>Memorias</t>
-  </si>
-  <si>
-    <t>mochilas</t>
-  </si>
-  <si>
-    <t>Mochilas</t>
-  </si>
-  <si>
-    <t>mouse</t>
-  </si>
-  <si>
-    <t>Mouse</t>
-  </si>
-  <si>
-    <t>muebles-armables</t>
-  </si>
-  <si>
-    <t>Muebles armables</t>
-  </si>
-  <si>
-    <t>mujer</t>
-  </si>
-  <si>
-    <t>Mujer</t>
-  </si>
-  <si>
-    <t>musica</t>
-  </si>
-  <si>
-    <t>Música</t>
-  </si>
-  <si>
-    <t>navidad</t>
-  </si>
-  <si>
-    <t>Navidad</t>
-  </si>
-  <si>
-    <t>nino</t>
-  </si>
-  <si>
-    <t>Niño</t>
-  </si>
-  <si>
-    <t>organizadores</t>
-  </si>
-  <si>
-    <t>Organizadores</t>
-  </si>
-  <si>
-    <t>papeleria</t>
-  </si>
-  <si>
-    <t>Papelería</t>
-  </si>
-  <si>
-    <t>partes-de-computadora</t>
-  </si>
-  <si>
-    <t>Partes de computadora</t>
-  </si>
-  <si>
-    <t>pedaleras</t>
-  </si>
-  <si>
-    <t>Pedaleras</t>
-  </si>
-  <si>
-    <t>pendientes</t>
-  </si>
-  <si>
-    <t>Pendientes</t>
-  </si>
-  <si>
-    <t>perros</t>
-  </si>
-  <si>
-    <t>Perros</t>
-  </si>
-  <si>
-    <t>pestanas</t>
-  </si>
-  <si>
-    <t>Pestañas</t>
-  </si>
-  <si>
-    <t>plomeria</t>
-  </si>
-  <si>
-    <t>Plomería</t>
-  </si>
-  <si>
-    <t>pulseras</t>
-  </si>
-  <si>
-    <t>Pulseras</t>
-  </si>
-  <si>
-    <t>relojes</t>
-  </si>
-  <si>
-    <t>Relojes</t>
-  </si>
-  <si>
-    <t>ropa</t>
-  </si>
-  <si>
-    <t>Ropa</t>
-  </si>
-  <si>
-    <t>series-led</t>
-  </si>
-  <si>
-    <t>Series LED</t>
-  </si>
-  <si>
-    <t>series-navidenas</t>
-  </si>
-  <si>
-    <t>Series navideñas</t>
-  </si>
-  <si>
-    <t>sets-de-bisuteria</t>
-  </si>
-  <si>
-    <t>Sets de bisutería</t>
-  </si>
-  <si>
-    <t>skincare</t>
-  </si>
-  <si>
-    <t>Skincare</t>
-  </si>
-  <si>
-    <t>suplementos</t>
-  </si>
-  <si>
-    <t>Suplementos</t>
-  </si>
-  <si>
-    <t>teclados</t>
-  </si>
-  <si>
-    <t>Teclados</t>
-  </si>
-  <si>
-    <t>tiras-led</t>
-  </si>
-  <si>
-    <t>Tiras LED</t>
-  </si>
-  <si>
-    <t>unas</t>
-  </si>
-  <si>
-    <t>Uñas</t>
-  </si>
-  <si>
-    <t>veterinario</t>
-  </si>
-  <si>
-    <t>Veterinario</t>
-  </si>
-  <si>
-    <t>videojuegos</t>
-  </si>
-  <si>
-    <t>Videojuegos</t>
-  </si>
-  <si>
-    <t>yoga</t>
-  </si>
-  <si>
-    <t>Yoga</t>
+    <t>Organizadores-Hogar</t>
   </si>
   <si>
     <t>tag_slug</t>
@@ -38483,11 +37991,11 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:D100"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="34.135" bestFit="true" customWidth="true" style="0"/>
-    <col min="2" max="2" width="34.135" bestFit="true" customWidth="true" style="0"/>
+    <col min="1" max="1" width="25.851" bestFit="true" customWidth="true" style="0"/>
+    <col min="2" max="2" width="25.851" bestFit="true" customWidth="true" style="0"/>
     <col min="3" max="3" width="9.10" bestFit="true" style="0"/>
     <col min="4" max="4" width="9.10" bestFit="true" style="0"/>
   </cols>
@@ -38505,791 +38013,159 @@
         <v>91</v>
       </c>
       <c r="B2" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" t="s">
+      <c r="B3" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
         <v>93</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B4" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" t="s">
+      <c r="B5" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
         <v>95</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B6" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" t="s">
+      <c r="B7" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
         <v>97</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B8" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" t="s">
+      <c r="B9" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
         <v>99</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B10" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7" t="s">
+      <c r="B11" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" t="s">
         <v>101</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B12" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8" t="s">
+      <c r="B13" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" t="s">
         <v>103</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B14" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9" t="s">
+      <c r="B15" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" t="s">
         <v>105</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B16" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" t="s">
         <v>106</v>
       </c>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" t="s">
+      <c r="B17" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18" t="s">
         <v>107</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B18" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19" t="s">
         <v>108</v>
       </c>
-    </row>
-    <row r="11" spans="1:4">
-      <c r="A11" t="s">
+      <c r="B19" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20" t="s">
         <v>109</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B20" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4">
+      <c r="A21" t="s">
         <v>110</v>
       </c>
-    </row>
-    <row r="12" spans="1:4">
-      <c r="A12" t="s">
-        <v>111</v>
-      </c>
-      <c r="B12" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4">
-      <c r="A13" t="s">
-        <v>113</v>
-      </c>
-      <c r="B13" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4">
-      <c r="A14" t="s">
-        <v>115</v>
-      </c>
-      <c r="B14" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4">
-      <c r="A15" t="s">
-        <v>117</v>
-      </c>
-      <c r="B15" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4">
-      <c r="A16" t="s">
-        <v>117</v>
-      </c>
-      <c r="B16" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4">
-      <c r="A17" t="s">
-        <v>119</v>
-      </c>
-      <c r="B17" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4">
-      <c r="A18" t="s">
-        <v>121</v>
-      </c>
-      <c r="B18" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4">
-      <c r="A19" t="s">
-        <v>123</v>
-      </c>
-      <c r="B19" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4">
-      <c r="A20" t="s">
-        <v>125</v>
-      </c>
-      <c r="B20" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4">
-      <c r="A21" t="s">
-        <v>127</v>
-      </c>
       <c r="B21" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4">
-      <c r="A22" t="s">
-        <v>129</v>
-      </c>
-      <c r="B22" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4">
-      <c r="A23" t="s">
-        <v>131</v>
-      </c>
-      <c r="B23" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4">
-      <c r="A24" t="s">
-        <v>133</v>
-      </c>
-      <c r="B24" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4">
-      <c r="A25" t="s">
-        <v>135</v>
-      </c>
-      <c r="B25" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4">
-      <c r="A26" t="s">
-        <v>137</v>
-      </c>
-      <c r="B26" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4">
-      <c r="A27" t="s">
-        <v>139</v>
-      </c>
-      <c r="B27" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4">
-      <c r="A28" t="s">
-        <v>141</v>
-      </c>
-      <c r="B28" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4">
-      <c r="A29" t="s">
-        <v>143</v>
-      </c>
-      <c r="B29" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4">
-      <c r="A30" t="s">
-        <v>145</v>
-      </c>
-      <c r="B30" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4">
-      <c r="A31" t="s">
-        <v>147</v>
-      </c>
-      <c r="B31" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4">
-      <c r="A32" t="s">
-        <v>149</v>
-      </c>
-      <c r="B32" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4">
-      <c r="A33" t="s">
-        <v>151</v>
-      </c>
-      <c r="B33" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4">
-      <c r="A34" t="s">
-        <v>153</v>
-      </c>
-      <c r="B34" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4">
-      <c r="A35" t="s">
-        <v>155</v>
-      </c>
-      <c r="B35" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4">
-      <c r="A36" t="s">
-        <v>155</v>
-      </c>
-      <c r="B36" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4">
-      <c r="A37" t="s">
-        <v>157</v>
-      </c>
-      <c r="B37" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4">
-      <c r="A38" t="s">
-        <v>159</v>
-      </c>
-      <c r="B38" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4">
-      <c r="A39" t="s">
-        <v>161</v>
-      </c>
-      <c r="B39" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4">
-      <c r="A40" t="s">
-        <v>163</v>
-      </c>
-      <c r="B40" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4">
-      <c r="A41" t="s">
-        <v>165</v>
-      </c>
-      <c r="B41" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4">
-      <c r="A42" t="s">
-        <v>167</v>
-      </c>
-      <c r="B42" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4">
-      <c r="A43" t="s">
-        <v>169</v>
-      </c>
-      <c r="B43" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4">
-      <c r="A44" t="s">
-        <v>171</v>
-      </c>
-      <c r="B44" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4">
-      <c r="A45" t="s">
-        <v>171</v>
-      </c>
-      <c r="B45" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4">
-      <c r="A46" t="s">
-        <v>171</v>
-      </c>
-      <c r="B46" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4">
-      <c r="A47" t="s">
-        <v>173</v>
-      </c>
-      <c r="B47" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4">
-      <c r="A48" t="s">
-        <v>175</v>
-      </c>
-      <c r="B48" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4">
-      <c r="A49" t="s">
-        <v>177</v>
-      </c>
-      <c r="B49" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4">
-      <c r="A50" t="s">
-        <v>179</v>
-      </c>
-      <c r="B50" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4">
-      <c r="A51" t="s">
-        <v>181</v>
-      </c>
-      <c r="B51" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4">
-      <c r="A52" t="s">
-        <v>183</v>
-      </c>
-      <c r="B52" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4">
-      <c r="A53" t="s">
-        <v>185</v>
-      </c>
-      <c r="B53" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4">
-      <c r="A54" t="s">
-        <v>187</v>
-      </c>
-      <c r="B54" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4">
-      <c r="A55" t="s">
-        <v>189</v>
-      </c>
-      <c r="B55" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4">
-      <c r="A56" t="s">
-        <v>191</v>
-      </c>
-      <c r="B56" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4">
-      <c r="A57" t="s">
-        <v>193</v>
-      </c>
-      <c r="B57" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4">
-      <c r="A58" t="s">
-        <v>195</v>
-      </c>
-      <c r="B58" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4">
-      <c r="A59" t="s">
-        <v>197</v>
-      </c>
-      <c r="B59" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="60" spans="1:4">
-      <c r="A60" t="s">
-        <v>199</v>
-      </c>
-      <c r="B60" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="61" spans="1:4">
-      <c r="A61" t="s">
-        <v>201</v>
-      </c>
-      <c r="B61" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="62" spans="1:4">
-      <c r="A62" t="s">
-        <v>203</v>
-      </c>
-      <c r="B62" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="63" spans="1:4">
-      <c r="A63" t="s">
-        <v>205</v>
-      </c>
-      <c r="B63" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="64" spans="1:4">
-      <c r="A64" t="s">
-        <v>207</v>
-      </c>
-      <c r="B64" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="65" spans="1:4">
-      <c r="A65" t="s">
-        <v>209</v>
-      </c>
-      <c r="B65" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="66" spans="1:4">
-      <c r="A66" t="s">
-        <v>211</v>
-      </c>
-      <c r="B66" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="67" spans="1:4">
-      <c r="A67" t="s">
-        <v>213</v>
-      </c>
-      <c r="B67" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="68" spans="1:4">
-      <c r="A68" t="s">
-        <v>215</v>
-      </c>
-      <c r="B68" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="69" spans="1:4">
-      <c r="A69" t="s">
-        <v>217</v>
-      </c>
-      <c r="B69" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="70" spans="1:4">
-      <c r="A70" t="s">
-        <v>219</v>
-      </c>
-      <c r="B70" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="71" spans="1:4">
-      <c r="A71" t="s">
-        <v>221</v>
-      </c>
-      <c r="B71" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="72" spans="1:4">
-      <c r="A72" t="s">
-        <v>223</v>
-      </c>
-      <c r="B72" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="73" spans="1:4">
-      <c r="A73" t="s">
-        <v>223</v>
-      </c>
-      <c r="B73" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="74" spans="1:4">
-      <c r="A74" t="s">
-        <v>223</v>
-      </c>
-      <c r="B74" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="75" spans="1:4">
-      <c r="A75" t="s">
-        <v>225</v>
-      </c>
-      <c r="B75" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="76" spans="1:4">
-      <c r="A76" t="s">
-        <v>227</v>
-      </c>
-      <c r="B76" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="77" spans="1:4">
-      <c r="A77" t="s">
-        <v>229</v>
-      </c>
-      <c r="B77" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="78" spans="1:4">
-      <c r="A78" t="s">
-        <v>229</v>
-      </c>
-      <c r="B78" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="79" spans="1:4">
-      <c r="A79" t="s">
-        <v>231</v>
-      </c>
-      <c r="B79" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="80" spans="1:4">
-      <c r="A80" t="s">
-        <v>233</v>
-      </c>
-      <c r="B80" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="81" spans="1:4">
-      <c r="A81" t="s">
-        <v>235</v>
-      </c>
-      <c r="B81" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="82" spans="1:4">
-      <c r="A82" t="s">
-        <v>237</v>
-      </c>
-      <c r="B82" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="83" spans="1:4">
-      <c r="A83" t="s">
-        <v>239</v>
-      </c>
-      <c r="B83" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="84" spans="1:4">
-      <c r="A84" t="s">
-        <v>241</v>
-      </c>
-      <c r="B84" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="85" spans="1:4">
-      <c r="A85" t="s">
-        <v>243</v>
-      </c>
-      <c r="B85" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="86" spans="1:4">
-      <c r="A86" t="s">
-        <v>245</v>
-      </c>
-      <c r="B86" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="87" spans="1:4">
-      <c r="A87" t="s">
-        <v>247</v>
-      </c>
-      <c r="B87" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="88" spans="1:4">
-      <c r="A88" t="s">
-        <v>249</v>
-      </c>
-      <c r="B88" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="89" spans="1:4">
-      <c r="A89" t="s">
-        <v>251</v>
-      </c>
-      <c r="B89" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="90" spans="1:4">
-      <c r="A90" t="s">
-        <v>253</v>
-      </c>
-      <c r="B90" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="91" spans="1:4">
-      <c r="A91" t="s">
-        <v>255</v>
-      </c>
-      <c r="B91" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="92" spans="1:4">
-      <c r="A92" t="s">
-        <v>257</v>
-      </c>
-      <c r="B92" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="93" spans="1:4">
-      <c r="A93" t="s">
-        <v>259</v>
-      </c>
-      <c r="B93" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="94" spans="1:4">
-      <c r="A94" t="s">
-        <v>261</v>
-      </c>
-      <c r="B94" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="95" spans="1:4">
-      <c r="A95" t="s">
-        <v>263</v>
-      </c>
-      <c r="B95" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="96" spans="1:4">
-      <c r="A96" t="s">
-        <v>265</v>
-      </c>
-      <c r="B96" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="97" spans="1:4">
-      <c r="A97" t="s">
-        <v>267</v>
-      </c>
-      <c r="B97" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="98" spans="1:4">
-      <c r="A98" t="s">
-        <v>269</v>
-      </c>
-      <c r="B98" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="99" spans="1:4">
-      <c r="A99" t="s">
-        <v>271</v>
-      </c>
-      <c r="B99" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="100" spans="1:4">
-      <c r="A100" t="s">
-        <v>273</v>
-      </c>
-      <c r="B100" t="s">
-        <v>274</v>
+        <v>110</v>
       </c>
     </row>
   </sheetData>
@@ -39324,7 +38200,7 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
-        <v>275</v>
+        <v>111</v>
       </c>
       <c r="B1" t="s">
         <v>90</v>
@@ -39362,21 +38238,21 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
-        <v>276</v>
+        <v>112</v>
       </c>
       <c r="B1" t="s">
-        <v>277</v>
+        <v>113</v>
       </c>
       <c r="C1" t="s">
-        <v>278</v>
+        <v>114</v>
       </c>
       <c r="D1" t="s">
-        <v>279</v>
+        <v>115</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>280</v>
+        <v>116</v>
       </c>
       <c r="B2" t="s">
         <v>54</v>
@@ -39385,7 +38261,7 @@
         <v>58</v>
       </c>
       <c r="D2" t="s">
-        <v>281</v>
+        <v>117</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -39393,7 +38269,7 @@
         <v>52</v>
       </c>
       <c r="B3" t="s">
-        <v>282</v>
+        <v>118</v>
       </c>
       <c r="D3" t="s">
         <v>60</v>
@@ -39432,13 +38308,13 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>283</v>
+        <v>119</v>
       </c>
       <c r="C1" t="s">
-        <v>284</v>
+        <v>120</v>
       </c>
       <c r="D1" t="s">
-        <v>285</v>
+        <v>121</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -39476,10 +38352,10 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
-        <v>286</v>
+        <v>122</v>
       </c>
       <c r="B1" t="s">
-        <v>287</v>
+        <v>123</v>
       </c>
       <c r="C1" t="s">
         <v>90</v>
@@ -39487,13 +38363,13 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>288</v>
+        <v>124</v>
       </c>
       <c r="B2" t="s">
-        <v>289</v>
+        <v>125</v>
       </c>
       <c r="C2" t="s">
-        <v>290</v>
+        <v>126</v>
       </c>
     </row>
   </sheetData>
